--- a/RAG Gemini/dataset_rag.xlsx
+++ b/RAG Gemini/dataset_rag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Computer Programming\Python\ML-Projects\RAG Gemini\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56FC0E82-2A9A-45D6-BC5F-D73D0B9FC37A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A67A458-7526-4A53-B789-8806E00DE08F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5436" yWindow="1992" windowWidth="17280" windowHeight="9420" xr2:uid="{199B9FFF-B56B-41A2-9075-2F768E528C36}"/>
   </bookViews>
